--- a/results/Int All Data 0.3/Rando_9_permute.xlsx
+++ b/results/Int All Data 0.3/Rando_9_permute.xlsx
@@ -440,897 +440,897 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9033400809716599</v>
+        <v>0.9033875964955674</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9033400809716599</v>
+        <v>0.9033875964955674</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9043522267206479</v>
+        <v>0.9033875964955674</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9043522267206479</v>
+        <v>0.9028815236210734</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9003036437246963</v>
+        <v>0.9028815236210734</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9003036437246963</v>
+        <v>0.9033875964955674</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9008097165991903</v>
+        <v>0.905917960868037</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9018218623481782</v>
+        <v>0.905917960868037</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9013157894736843</v>
+        <v>0.9064240337425309</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9013157894736843</v>
+        <v>0.9064240337425309</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9018218623481782</v>
+        <v>0.9064240337425309</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9058704453441295</v>
+        <v>0.9064240337425309</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9104251012145749</v>
+        <v>0.9049058151190492</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9078947368421053</v>
+        <v>0.9038936693700613</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9084008097165992</v>
+        <v>0.9038936693700613</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9084008097165992</v>
+        <v>0.9038936693700613</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9084008097165992</v>
+        <v>0.9069301066170249</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9078947368421053</v>
+        <v>0.9069301066170249</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9063765182186234</v>
+        <v>0.9069301066170249</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9048582995951417</v>
+        <v>0.9069301066170249</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9023279352226721</v>
+        <v>0.9069301066170249</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9003036437246963</v>
+        <v>0.9069301066170249</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9013157894736843</v>
+        <v>0.905917960868037</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9013157894736843</v>
+        <v>0.905917960868037</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9030185375632998</v>
+        <v>0.905917960868037</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9023754507465795</v>
+        <v>0.9054118879935431</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.9018693778720857</v>
+        <v>0.9054118879935431</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9043102438262364</v>
+        <v>0.9028815236210734</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9043102438262364</v>
+        <v>0.9038936693700613</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9055964174596769</v>
+        <v>0.9028815236210734</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.882182329432287</v>
+        <v>0.901595349987633</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8825038728406472</v>
+        <v>0.9021014228621269</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8793890024343569</v>
+        <v>0.9035721259617011</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8755304815340355</v>
+        <v>0.9026969941549396</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.869832198601872</v>
+        <v>0.9033400809716599</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8725360271814833</v>
+        <v>0.9033400809716599</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8761205201973521</v>
+        <v>0.8704453441295547</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8753404194384056</v>
+        <v>0.8704453441295547</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8689570667951105</v>
+        <v>0.8679149797570851</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8684985094445239</v>
+        <v>0.8679149797570851</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8693736412512856</v>
+        <v>0.8679149797570851</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8675338792194436</v>
+        <v>0.8679149797570851</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8668432768788159</v>
+        <v>0.8674089068825911</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8568754312196518</v>
+        <v>0.8658906882591093</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8506290925185831</v>
+        <v>0.8653846153846154</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8486998320684224</v>
+        <v>0.8593117408906883</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8430070817657549</v>
+        <v>0.8594962703568221</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8423109467956311</v>
+        <v>0.8537449392712551</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8471816134449406</v>
+        <v>0.8557692307692308</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8462169832198603</v>
+        <v>0.8552631578947368</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8462644987437676</v>
+        <v>0.8567813765182186</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8470921150266217</v>
+        <v>0.8572874493927125</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8462169832198603</v>
+        <v>0.877451931213143</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8391374956064412</v>
+        <v>0.8696343257351888</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8375297785646406</v>
+        <v>0.8697293567830038</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8355054870666649</v>
+        <v>0.8692232839085099</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8346778707838109</v>
+        <v>0.8703304607053126</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8344933413176771</v>
+        <v>0.8695028444224586</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8398645482119843</v>
+        <v>0.8695028444224586</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8395010219092128</v>
+        <v>0.8661028808727235</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8344878086881811</v>
+        <v>0.8625603707512659</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8314569040707135</v>
+        <v>0.8641261048986553</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8295751591444602</v>
+        <v>0.8641261048986553</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8186426832602158</v>
+        <v>0.8648167072392829</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.815474764700522</v>
+        <v>0.8610896676516917</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8174040251506828</v>
+        <v>0.865218961948527</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.815474764700522</v>
+        <v>0.8644808440839918</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8129974484814559</v>
+        <v>0.8633316843927776</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8149267089316167</v>
+        <v>0.8751614226017679</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.8228282801983936</v>
+        <v>0.8768387856854603</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8180526445968991</v>
+        <v>0.877945962482263</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8157012770610672</v>
+        <v>0.8768863012093677</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8276878815887108</v>
+        <v>0.8732123097751799</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8213575770988193</v>
+        <v>0.8665074137235247</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.8174515406745902</v>
+        <v>0.8676565734147389</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.8174515406745902</v>
+        <v>0.8677880547274692</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.8361850241483005</v>
+        <v>0.867556009737428</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.832010492469115</v>
+        <v>0.8615726336618197</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.8336126768814195</v>
+        <v>0.8612510902534596</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.8358214978455289</v>
+        <v>0.8602246247575407</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.8353574078654464</v>
+        <v>0.8552169441660049</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.8386203574729552</v>
+        <v>0.8542047984170171</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.82627022664254</v>
+        <v>0.8524125519090826</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.8249420701146881</v>
+        <v>0.8519959774529076</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.8249420701146881</v>
+        <v>0.8423386099431116</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.8230128096645274</v>
+        <v>0.8423386099431116</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.8230128096645274</v>
+        <v>0.8451794524649492</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.8195653305908848</v>
+        <v>0.8388071650806461</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.8205299608159653</v>
+        <v>0.8393132379551401</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.8175996198758088</v>
+        <v>0.8431717588554617</v>
       </c>
     </row>
     <row r="92">
@@ -1340,467 +1340,467 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.8187123293021076</v>
+        <v>0.8342271242042777</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.8187123293021076</v>
+        <v>0.8370315164612</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.8187123293021076</v>
+        <v>0.8373221422341408</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.8160029680930003</v>
+        <v>0.8342437220927659</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.8115488758998659</v>
+        <v>0.8413176770766888</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.807136766601143</v>
+        <v>0.8391199213715714</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.8041478448780869</v>
+        <v>0.8334746865928115</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.8051124751031673</v>
+        <v>0.8264007316088886</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.800663915539529</v>
+        <v>0.8315454261426507</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.8059876069099288</v>
+        <v>0.8390248903237565</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.8103466680552482</v>
+        <v>0.8318669695510108</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.8103466680552482</v>
+        <v>0.8318669695510108</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.7996462371610451</v>
+        <v>0.8242029759037713</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.799324693752685</v>
+        <v>0.8250305921866253</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.8005213689678066</v>
+        <v>0.8203919705273572</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.8005213689678066</v>
+        <v>0.8147135399716209</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.8071787494955543</v>
+        <v>0.8335475871226421</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.8086439199656326</v>
+        <v>0.8389187940169494</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.8125499563898616</v>
+        <v>0.8322304958537823</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.8125499563898616</v>
+        <v>0.7818718512829191</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.8125499563898616</v>
+        <v>0.7739813452751344</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.8249531353736803</v>
+        <v>0.7761846336097478</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.8238768762122968</v>
+        <v>0.7835967298905191</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.8271928739732091</v>
+        <v>0.7250348230209459</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.8223697228478071</v>
+        <v>0.7085078823697879</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.8217266360310869</v>
+        <v>0.703790827551193</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.8344933413176771</v>
+        <v>0.7051577124855175</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.8217741515549943</v>
+        <v>0.6619361599645912</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.8285630133954723</v>
+        <v>0.6734023718708099</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.8304447583217256</v>
+        <v>0.6724377416457294</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.8309508311962196</v>
+        <v>0.6698598617493523</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.8309508311962196</v>
+        <v>0.6507683846023666</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.6933800460835492</v>
+        <v>0.6548036241977687</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.6933800460835492</v>
+        <v>0.6485462202377078</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.6765702904305037</v>
+        <v>0.5332481742322663</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.6218460757384433</v>
+        <v>0.5060175481989664</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.6220670554694925</v>
+        <v>0.5168605256648918</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.6012672976033951</v>
+        <v>0.5193013916190427</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.6019578999440228</v>
+        <v>0.5167853469935041</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5887183175599151</v>
+        <v>0.514212999726623</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5692522488511658</v>
+        <v>0.5052992827108582</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5660368147675645</v>
+        <v>0.5052992827108582</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5397233034354374</v>
+        <v>0.5034120051551089</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5424326646445449</v>
+        <v>0.5205179192105914</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5424326646445449</v>
+        <v>0.5205179192105914</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5424326646445449</v>
+        <v>0.5116042021948267</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5465707460588151</v>
+        <v>0.5116042021948267</v>
       </c>
     </row>
     <row r="139">
@@ -1810,177 +1810,177 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5465707460588151</v>
+        <v>0.5096749417446659</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5465707460588151</v>
+        <v>0.5290957730710649</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5588733613653227</v>
+        <v>0.5278990978559434</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5866045276436206</v>
+        <v>0.5269344676308629</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5760466433211399</v>
+        <v>0.5196340002863949</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.7102705130374787</v>
+        <v>0.5133092284259995</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.7102705130374787</v>
+        <v>0.5049490998086361</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.7119843263860864</v>
+        <v>0.5112849369280237</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5895514664722652</v>
+        <v>0.5047756356014945</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5962983454183318</v>
+        <v>0.5039480193186404</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5938630120936772</v>
+        <v>0.5039480193186404</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.6227488706926853</v>
+        <v>0.5039480193186404</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.6389630550529179</v>
+        <v>0.503489461968054</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.4846417459676894</v>
+        <v>0.5028463751513337</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5160768449692126</v>
+        <v>0.5031679185596938</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5137397971803117</v>
+        <v>0.5028463751513337</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5057985211606806</v>
+        <v>0.501649699936212</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5057985211606806</v>
+        <v>0.5003215434083601</v>
       </c>
     </row>
   </sheetData>
